--- a/sources/table_normalization/xlsx/economy-table96.xlsx
+++ b/sources/table_normalization/xlsx/economy-table96.xlsx
@@ -385,24 +385,9 @@
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -415,12 +400,27 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,68 +744,68 @@
       <c r="M1" s="8"/>
     </row>
     <row r="2" spans="1:13" ht="50" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="G2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="18" t="s">
+      <c r="H2" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="18" t="s">
+      <c r="I2" s="26"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="18"/>
-      <c r="M2" s="19"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="27"/>
     </row>
     <row r="3" spans="1:13" ht="13" x14ac:dyDescent="0.3">
       <c r="A3" s="20"/>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="23" t="s">
+      <c r="I3" s="16"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="23"/>
-      <c r="M3" s="24"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="17"/>
     </row>
     <row r="4" spans="1:13" ht="13" x14ac:dyDescent="0.3">
       <c r="A4" s="20"/>
@@ -814,46 +814,46 @@
       <c r="D4" s="20"/>
       <c r="E4" s="20"/>
       <c r="F4" s="20"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="21"/>
+      <c r="H4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="26" t="s">
+      <c r="K4" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="26" t="s">
+      <c r="L4" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="18">
         <v>0.2</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="18">
         <v>0.1</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="18">
         <v>-3.5</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="18">
         <v>26.7</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="18">
         <v>-10.3</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="19">
         <v>4.3</v>
       </c>
       <c r="H5" s="1" t="s">
@@ -958,591 +958,591 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="14"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="19"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="18">
         <v>-3.6</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="18">
         <v>3.3</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="18">
         <v>10.8</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="18">
         <v>18.100000000000001</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="18">
         <v>22</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="19">
         <v>4.4000000000000004</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="18">
         <v>8.1999999999999993</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="18">
         <v>10.7</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="19">
         <v>13.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="18">
         <v>-19.3</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="18">
         <v>-0.9</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="19">
         <v>21.5</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="18">
         <v>-0.5</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="18">
         <v>-0.1</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="18">
         <v>4.9000000000000004</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="18">
         <v>-5.2</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="18">
         <v>13.5</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="19">
         <v>4.2</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="18">
         <v>0.6</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="18">
         <v>4.3</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="19">
         <v>8.8000000000000007</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="18">
         <v>-19.7</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="18">
         <v>0.2</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="19">
         <v>25.7</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="14"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="18">
         <v>0.8</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="18">
         <v>13.1</v>
       </c>
-      <c r="D12" s="1">
+      <c r="D12" s="18">
         <v>11.2</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="18">
         <v>-2.2000000000000002</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="18">
         <v>-3.7</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="19">
         <v>2.2000000000000002</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="18">
         <v>8.8000000000000007</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="18">
         <v>11.9</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="19">
         <v>15.3</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="18">
         <v>-19.899999999999999</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="18">
         <v>2.1</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="19">
         <v>30.4</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="14"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="19"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="18">
         <v>9.1</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="18">
         <v>6.3</v>
       </c>
-      <c r="D14" s="1">
+      <c r="D14" s="18">
         <v>0.3</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="18">
         <v>17.3</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="18">
         <v>-18</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="19">
         <v>2.5</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="18">
         <v>1.3</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="18">
         <v>3.3</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="19">
         <v>5.3</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="18">
         <v>-8.4</v>
       </c>
-      <c r="L14" s="1">
+      <c r="L14" s="18">
         <v>10.8</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="19">
         <v>34.700000000000003</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="14"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="18">
         <v>-7.3</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="18">
         <v>124.3</v>
       </c>
-      <c r="D16" s="1">
+      <c r="D16" s="18">
         <v>30</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="18">
         <v>163.1</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="18">
         <v>-28.3</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="19">
         <v>11.7</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="18">
         <v>22.2</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="18">
         <v>39.200000000000003</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="19">
         <v>68</v>
       </c>
-      <c r="K16" s="1">
+      <c r="K16" s="18">
         <v>-49.1</v>
       </c>
-      <c r="L16" s="1">
+      <c r="L16" s="18">
         <v>31.3</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="19">
         <v>260.2</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="14"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="19"/>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="18">
         <v>1.3</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="18">
         <v>13.9</v>
       </c>
-      <c r="D18" s="1">
+      <c r="D18" s="18">
         <v>6.9</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="18">
         <v>36.700000000000003</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="18">
         <v>-19.899999999999999</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="19">
         <v>4.5999999999999996</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="18">
         <v>4.8</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="18">
         <v>9</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="19">
         <v>13.7</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="18">
         <v>-24.2</v>
       </c>
-      <c r="L18" s="1">
+      <c r="L18" s="18">
         <v>6.3</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="19">
         <v>50.6</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="18">
         <v>1.5</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="18">
         <v>7.8</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D19" s="18">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="18">
         <v>18.3</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="18">
         <v>-6.1</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="19">
         <v>2.9</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="18">
         <v>2.4</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="18">
         <v>3.9</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="19">
         <v>5.4</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="18">
         <v>-8.6</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L19" s="18">
         <v>5.3</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="19">
         <v>21.5</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="14"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="19"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="18">
         <v>-1.6</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="18">
         <v>-27.1</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" s="18">
         <v>-19.7</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="18">
         <v>11.2</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="18">
         <v>-8.3000000000000007</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="19">
         <v>5.9</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="18">
         <v>-25.1</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="18">
         <v>-22.5</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="19">
         <v>-19.600000000000001</v>
       </c>
-      <c r="K21" s="1">
+      <c r="K21" s="18">
         <v>-36.200000000000003</v>
       </c>
-      <c r="L21" s="1">
+      <c r="L21" s="18">
         <v>-11.6</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="19">
         <v>25.1</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="18">
         <v>-0.8</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="18">
         <v>-10.4</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D22" s="18">
         <v>-10.199999999999999</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="18">
         <v>26.1</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="18">
         <v>-16.3</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="19">
         <v>5.6</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="18">
         <v>-12.3</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="18">
         <v>-11</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="19">
         <v>-9.6999999999999993</v>
       </c>
-      <c r="K22" s="1">
+      <c r="K22" s="18">
         <v>-24.4</v>
       </c>
-      <c r="L22" s="1">
+      <c r="L22" s="18">
         <v>-7.1</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="19">
         <v>14.6</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="14"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+      <c r="M23" s="19"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="18">
         <v>8.3000000000000007</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="18">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" s="18">
         <v>-5.2</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="18">
         <v>18.100000000000001</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="18">
         <v>-0.6</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="19">
         <v>4</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="18">
         <v>-7.3</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="18">
         <v>-4.5999999999999996</v>
       </c>
-      <c r="J24" s="5">
+      <c r="J24" s="19">
         <v>-1.6</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="18">
         <v>-11.4</v>
       </c>
-      <c r="L24" s="1">
+      <c r="L24" s="18">
         <v>1.9</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="19">
         <v>17.5</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="18">
         <v>-2.5</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="18">
         <v>7.7</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" s="18">
         <v>-2.5</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="18">
         <v>51.4</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="18">
         <v>-12.1</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="19">
         <v>5</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="18">
         <v>-8.9</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="18">
         <v>-3.5</v>
       </c>
-      <c r="J25" s="5">
+      <c r="J25" s="19">
         <v>3.6</v>
       </c>
-      <c r="K25" s="1">
+      <c r="K25" s="18">
         <v>-27.1</v>
       </c>
-      <c r="L25" s="1">
+      <c r="L25" s="18">
         <v>-3.5</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="19">
         <v>29.1</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="14"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="19"/>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
